--- a/DRIVE/3. Operações/3.1 Projetos/26003 - CAFE TRINDADE 1961 (São João da Madeira)/Peças escritas/PRÉ-ORÇAMENTO LB V1 SAO-2026-0003-ESPL.xlsx
+++ b/DRIVE/3. Operações/3.1 Projetos/26003 - CAFE TRINDADE 1961 (São João da Madeira)/Peças escritas/PRÉ-ORÇAMENTO LB V1 SAO-2026-0003-ESPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\3. Operações\3.1 Projetos\26003 - CAFE TRINDADE 1961 (São João da Madeira)\Peças escritas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1B97CD-056C-4679-A735-12C9368358FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49FF32C-BBDC-49C1-8549-BBDEB1B23639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -136,12 +136,6 @@
     <t>Coluna passiva 2 vias 16,5cm 30W RMS, 8Ω, c/ suporte parede, indoor</t>
   </si>
   <si>
-    <t>Amplificador de potência Class AB, 2×150W RMS 4Ω, input: XLR  / jack</t>
-  </si>
-  <si>
-    <t>Cabo paralelo bobine — 100m, 8.0 mm</t>
-  </si>
-  <si>
     <t>Mao de obra especializada, prazo de entrega: 1 dia.</t>
   </si>
   <si>
@@ -149,6 +143,12 @@
   </si>
   <si>
     <t>PROPOSTA DE FORNECIMENTO (MAIS BARATO)</t>
+  </si>
+  <si>
+    <t>Amplificador de potência Class AB, 2×150W RMS @ 4Ω</t>
+  </si>
+  <si>
+    <t>Cabo paralelo bobine — 100m</t>
   </si>
 </sst>
 </file>
@@ -613,6 +613,15 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -633,15 +642,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -967,7 +967,7 @@
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
     <col min="7" max="7" width="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -977,10 +977,10 @@
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
       <c r="D2" s="39"/>
-      <c r="E2" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="65"/>
+      <c r="E2" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="58"/>
       <c r="G2" s="40"/>
     </row>
     <row r="3" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1010,7 +1010,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="20">
-        <v>46137</v>
+        <v>46152</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="22" t="s">
@@ -1092,7 +1092,7 @@
     </row>
     <row r="11" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="60">
+      <c r="B11" s="63">
         <v>2</v>
       </c>
       <c r="C11" s="9"/>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="60"/>
+      <c r="B12" s="63"/>
       <c r="C12" s="6" t="s">
         <v>22</v>
       </c>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="61"/>
+      <c r="B13" s="64"/>
       <c r="C13" s="36" t="s">
         <v>31</v>
       </c>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="14" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="62">
+      <c r="B14" s="65">
         <v>1</v>
       </c>
       <c r="C14" s="9"/>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="60"/>
+      <c r="B15" s="63"/>
       <c r="C15" s="6" t="s">
         <v>23</v>
       </c>
@@ -1165,9 +1165,9 @@
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="61"/>
+      <c r="B16" s="64"/>
       <c r="C16" s="36" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
@@ -1176,7 +1176,7 @@
     </row>
     <row r="17" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="62">
+      <c r="B17" s="65">
         <v>1</v>
       </c>
       <c r="C17" s="9"/>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="60"/>
+      <c r="B18" s="63"/>
       <c r="C18" s="6" t="s">
         <v>24</v>
       </c>
@@ -1207,9 +1207,9 @@
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="61"/>
+      <c r="B19" s="64"/>
       <c r="C19" s="36" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D19" s="31"/>
       <c r="E19" s="31"/>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="20" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="62">
+      <c r="B20" s="65">
         <v>1</v>
       </c>
       <c r="C20" s="9"/>
@@ -1229,11 +1229,11 @@
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="60"/>
+      <c r="B21" s="63"/>
       <c r="C21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="63">
+      <c r="D21" s="56">
         <f>180*1.3</f>
         <v>234</v>
       </c>
@@ -1249,9 +1249,9 @@
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="61"/>
+      <c r="B22" s="64"/>
       <c r="C22" s="36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D22" s="31"/>
       <c r="E22" s="31"/>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="23" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="62">
+      <c r="B23" s="65">
         <v>1</v>
       </c>
       <c r="C23" s="9"/>
@@ -1271,11 +1271,11 @@
     </row>
     <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="60"/>
+      <c r="B24" s="63"/>
       <c r="C24" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="64">
+      <c r="D24" s="57">
         <f>61.54*1.3</f>
         <v>80.001999999999995</v>
       </c>
@@ -1291,9 +1291,9 @@
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="61"/>
+      <c r="B25" s="64"/>
       <c r="C25" s="36" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
@@ -1463,15 +1463,15 @@
       <c r="G60" s="2"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="56" t="s">
+      <c r="A61" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="58"/>
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="61"/>
     </row>
     <row r="62" spans="1:7" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="33"/>
@@ -1488,11 +1488,11 @@
         <v>7</v>
       </c>
       <c r="C63" s="52"/>
-      <c r="D63" s="59" t="s">
+      <c r="D63" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="E63" s="59"/>
-      <c r="F63" s="59"/>
+      <c r="E63" s="62"/>
+      <c r="F63" s="62"/>
       <c r="G63" s="53"/>
     </row>
   </sheetData>
